--- a/artfynd/A 927-2022 artfynd.xlsx
+++ b/artfynd/A 927-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 927-2022 artfynd.xlsx
+++ b/artfynd/A 927-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>86950556</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502286.3757037192</v>
+        <v>502286</v>
       </c>
       <c r="R2" t="n">
-        <v>6668748.252709548</v>
+        <v>6668748</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,19 +759,9 @@
           <t>2020-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
